--- a/Lab-trails/2026-04-29-cattle-slurry-retrail/2026-04-29-CattleSlurryRetry-slurry.xlsx
+++ b/Lab-trails/2026-04-29-cattle-slurry-retrail/2026-04-29-CattleSlurryRetry-slurry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-04-29-cattle-slurry-retrail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DFB7B9-65B1-4CF6-8F29-44A0684698F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F347594F-078D-4625-B8F4-A321F5E03EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TAN" sheetId="1" r:id="rId1"/>
@@ -1109,7 +1109,8 @@
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="5" width="13.33203125" customWidth="1"/>
+    <col min="2" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">

--- a/Lab-trails/2026-04-29-cattle-slurry-retrail/2026-04-29-CattleSlurryRetry-slurry.xlsx
+++ b/Lab-trails/2026-04-29-cattle-slurry-retrail/2026-04-29-CattleSlurryRetry-slurry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-04-29-cattle-slurry-retrail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F347594F-078D-4625-B8F4-A321F5E03EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F5C2162-7CCD-4D5A-9539-F56EA5EADD4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="288" windowWidth="23232" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TAN" sheetId="1" r:id="rId1"/>
@@ -60,6 +60,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={C51D159F-E2C0-41C0-887A-301B07363DDC}</author>
+    <author>tc={42CB89A3-3418-4C2F-8452-3DC8C5FBE2D4}</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0" xr:uid="{C51D159F-E2C0-41C0-887A-301B07363DDC}">
@@ -68,6 +69,14 @@
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     The day before the start of the experiment</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{42CB89A3-3418-4C2F-8452-3DC8C5FBE2D4}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    This is key in understanding the variability I belive - the treatments aren’t stable at lab-scale</t>
       </text>
     </comment>
   </commentList>
@@ -223,7 +232,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,6 +247,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -568,6 +583,9 @@
   <threadedComment ref="B1" dT="2026-04-29T09:06:30.61" personId="{FCAAED7B-F5F1-4553-9146-85CC0A69F825}" id="{C51D159F-E2C0-41C0-887A-301B07363DDC}">
     <text>The day before the start of the experiment</text>
   </threadedComment>
+  <threadedComment ref="E1" dT="2026-05-06T08:01:13.85" personId="{FCAAED7B-F5F1-4553-9146-85CC0A69F825}" id="{42CB89A3-3418-4C2F-8452-3DC8C5FBE2D4}">
+    <text>This is key in understanding the variability I belive - the treatments aren’t stable at lab-scale</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -955,7 +973,17 @@
         <f>C2-B2</f>
         <v>30.158000000000001</v>
       </c>
-      <c r="G2" s="2"/>
+      <c r="E2">
+        <v>5.8949999999999996</v>
+      </c>
+      <c r="F2">
+        <f>E2-B2</f>
+        <v>2.1199999999999997</v>
+      </c>
+      <c r="G2" s="2">
+        <f>(F2/D2)*100</f>
+        <v>7.0296438755885653</v>
+      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -971,8 +999,17 @@
         <f t="shared" ref="D3:D10" si="0">C3-B3</f>
         <v>46.610999999999997</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="E3" s="2">
+        <v>7.0960000000000001</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F10" si="1">E3-B3</f>
+        <v>3.331</v>
+      </c>
+      <c r="G3" s="2">
+        <f t="shared" ref="G3:G10" si="2">(F3/D3)*100</f>
+        <v>7.1463817553796316</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -988,14 +1025,24 @@
         <f t="shared" si="0"/>
         <v>46.064</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="4" t="e">
+      <c r="E4">
+        <v>6.9790000000000001</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>3.2290000000000001</v>
+      </c>
+      <c r="G4" s="2">
+        <f t="shared" si="2"/>
+        <v>7.0098124348732194</v>
+      </c>
+      <c r="H4" s="3">
         <f>AVERAGE(G2:G4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I4" s="2" t="e">
+        <v>7.0619460219471391</v>
+      </c>
+      <c r="I4" s="2">
         <f>_xlfn.STDEV.P(G2:G4)</f>
-        <v>#DIV/0!</v>
+        <v>6.0251507977940898E-2</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -1012,7 +1059,17 @@
         <f t="shared" si="0"/>
         <v>30.122</v>
       </c>
-      <c r="G5" s="2"/>
+      <c r="E5">
+        <v>5.9059999999999997</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>2.1309999999999998</v>
+      </c>
+      <c r="G5" s="2">
+        <f t="shared" si="2"/>
+        <v>7.0745634420025221</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -1028,8 +1085,17 @@
         <f t="shared" si="0"/>
         <v>48.844000000000001</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="E6" s="2">
+        <v>7.2380000000000004</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>3.4730000000000003</v>
+      </c>
+      <c r="G6" s="2">
+        <f t="shared" si="2"/>
+        <v>7.1103922692654171</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -1045,9 +1111,25 @@
         <f t="shared" si="0"/>
         <v>37.258000000000003</v>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="2"/>
+      <c r="E7">
+        <v>6.3810000000000002</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>2.6180000000000003</v>
+      </c>
+      <c r="G7" s="2">
+        <f t="shared" si="2"/>
+        <v>7.026678834075903</v>
+      </c>
+      <c r="H7" s="4">
+        <f>AVERAGE(G5:G7)</f>
+        <v>7.0705448484479474</v>
+      </c>
+      <c r="I7" s="2">
+        <f>_xlfn.STDEV.P(G5:G7)</f>
+        <v>3.4293795633465997E-2</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -1063,7 +1145,17 @@
         <f t="shared" si="0"/>
         <v>48.002000000000002</v>
       </c>
-      <c r="G8" s="2"/>
+      <c r="E8">
+        <v>7.0279999999999996</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>3.2749999999999995</v>
+      </c>
+      <c r="G8" s="2">
+        <f t="shared" si="2"/>
+        <v>6.822632390317068</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -1079,7 +1171,17 @@
         <f t="shared" si="0"/>
         <v>49.721999999999994</v>
       </c>
-      <c r="G9" s="2"/>
+      <c r="E9">
+        <v>7.2009999999999996</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>3.4519999999999995</v>
+      </c>
+      <c r="G9" s="2">
+        <f t="shared" si="2"/>
+        <v>6.9426008607859702</v>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -1095,7 +1197,17 @@
         <f t="shared" si="0"/>
         <v>57.423000000000002</v>
       </c>
-      <c r="G10" s="2"/>
+      <c r="E10">
+        <v>7.8159999999999998</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>4.0659999999999998</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" si="2"/>
+        <v>7.080786444456054</v>
+      </c>
       <c r="H10" s="4"/>
       <c r="I10" s="2"/>
     </row>
